--- a/assets/ESR Unit Stats-English Units.xlsx
+++ b/assets/ESR Unit Stats-English Units.xlsx
@@ -5,17 +5,30 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\toddp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35739C65-C92B-49CB-8B46-27C72035736A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{35739C65-C92B-49CB-8B46-27C72035736A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A7ED55D-9F2D-41C6-AAB0-CA9B9BA0AA18}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="690" windowWidth="28590" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21285" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -98,105 +111,38 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>900 yds</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>450 yds</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Open Terrain</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Embarrassing Terrain</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Foot Guards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Infantry Battalion</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>–</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1 1/2</t>
-    </r>
+    <t>900 yds</t>
+  </si>
+  <si>
+    <t>450 yds</t>
+  </si>
+  <si>
+    <t>Open Terrain</t>
+  </si>
+  <si>
+    <t>Embarrassing Terrain</t>
+  </si>
+  <si>
+    <t>Foot Guards</t>
+  </si>
+  <si>
+    <t>Infantry Battalion</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>1 1/2</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <i/>
-        <sz val="6.5"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -204,7 +150,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="6.5"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -212,61 +158,26 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Life Guards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cavalry Squadron Group</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Royal Horse Guards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Light Infantry</t>
-    </r>
+    <t>Life Guards</t>
+  </si>
+  <si>
+    <t>Cavalry Squadron Group</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>Royal Horse Guards</t>
+  </si>
+  <si>
+    <t>Light Infantry</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <i/>
-        <sz val="6.5"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -274,7 +185,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="6.5"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -282,91 +193,35 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Foot Infantry</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Highland Foot Inf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fusilier Foot Infantry</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Rifles</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Infantry Company</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dragoon Guards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dragoons</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Light Dragoons</t>
-    </r>
+    <t>Foot Infantry</t>
+  </si>
+  <si>
+    <t>Highland Foot Inf</t>
+  </si>
+  <si>
+    <t>Fusilier Foot Infantry</t>
+  </si>
+  <si>
+    <t>Rifles</t>
+  </si>
+  <si>
+    <t>Infantry Company</t>
+  </si>
+  <si>
+    <t>Dragoon Guards</t>
+  </si>
+  <si>
+    <t>Dragoons</t>
+  </si>
+  <si>
+    <t>Light Dragoons</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <i/>
-        <sz val="6.5"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -374,7 +229,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="6.5"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -382,91 +237,31 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hussars</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>9-pdr Royal Artillery</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Artillery Battery (Asset)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>6-pdr Royal Artillery</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>6-pdr Royal Horse Artillery</t>
-    </r>
+    <t>Hussars</t>
+  </si>
+  <si>
+    <t>9-pdr Royal Artillery</t>
+  </si>
+  <si>
+    <t>Artillery Battery (Asset)</t>
+  </si>
+  <si>
+    <t>6-pdr Royal Artillery</t>
+  </si>
+  <si>
+    <t>6-pdr Royal Horse Artillery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="6.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="6.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="6.5"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -480,14 +275,38 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="6.5"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <i/>
-      <sz val="6.5"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -583,33 +402,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -625,8 +423,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -935,8 +754,8 @@
   <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.1640625" customWidth="1"/>
     <col min="4" max="4" width="15.1640625" customWidth="1"/>
     <col min="5" max="5" width="16.1640625" customWidth="1"/>
@@ -947,17 +766,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -966,442 +785,442 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="14"/>
+      <c r="D2" s="7"/>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="15">
         <v>4</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="16" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="C5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="15">
         <v>4</v>
       </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="15">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="10"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="C6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="15">
         <v>4</v>
       </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="15">
+        <v>1</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="C7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15">
         <v>3</v>
       </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="F7" s="15">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="15">
         <v>3</v>
       </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="15">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="15">
         <v>3</v>
       </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="15">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="16" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="15">
         <v>3</v>
       </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="15">
+        <v>1</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="16" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="11"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="C12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="15">
         <v>3</v>
       </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="15">
+        <v>1</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="10"/>
+      <c r="H12" s="17"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="C13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="15">
         <v>3</v>
       </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="15">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="10"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="C14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="15">
         <v>2</v>
       </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="15">
+        <v>1</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="16" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="C15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="15">
         <v>2</v>
       </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="16" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="15">
         <v>2</v>
       </c>
-      <c r="F16" s="8">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="15">
+        <v>1</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="10"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="15">
         <v>2</v>
       </c>
-      <c r="F17" s="8">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="15">
+        <v>1</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="15">
         <v>2</v>
       </c>
-      <c r="F18" s="8">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="15">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="10"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17">
-        <v>1</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
